--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_07/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_07/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>64.69</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54</v>
+        <v>16.62</v>
       </c>
       <c r="E2" t="n">
-        <v>27.11</v>
+        <v>25.25</v>
       </c>
       <c r="F2" t="n">
-        <v>44.06</v>
+        <v>45.85</v>
       </c>
       <c r="G2" t="n">
-        <v>49.08</v>
+        <v>51.05</v>
       </c>
       <c r="H2" t="n">
-        <v>59.93</v>
+        <v>62.3</v>
       </c>
       <c r="I2" t="n">
-        <v>78.51000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>55.94</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>45.97</v>
+        <v>45.71</v>
       </c>
       <c r="D3" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>45.92</v>
+        <v>45.63</v>
       </c>
       <c r="G3" t="n">
-        <v>45.93</v>
+        <v>45.63</v>
       </c>
       <c r="H3" t="n">
-        <v>45.93</v>
+        <v>45.64</v>
       </c>
       <c r="I3" t="n">
-        <v>45.96</v>
+        <v>45.66</v>
       </c>
       <c r="J3" t="n">
-        <v>46.54</v>
+        <v>47.04</v>
       </c>
       <c r="K3" t="n">
-        <v>0.62</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>9.369999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="E4" t="n">
-        <v>16.98</v>
+        <v>17.46</v>
       </c>
       <c r="F4" t="n">
-        <v>7.17</v>
+        <v>7.72</v>
       </c>
       <c r="G4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H4" t="n">
-        <v>8.85</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>10.7</v>
+        <v>11.61</v>
       </c>
       <c r="J4" t="n">
-        <v>12.32</v>
+        <v>12.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>95.70999999999999</v>
+        <v>105.25</v>
       </c>
       <c r="D5" t="n">
-        <v>14.74</v>
+        <v>38.32</v>
       </c>
       <c r="E5" t="n">
-        <v>15.4</v>
+        <v>36.41</v>
       </c>
       <c r="F5" t="n">
-        <v>67.84</v>
+        <v>66.45</v>
       </c>
       <c r="G5" t="n">
-        <v>83.65000000000001</v>
+        <v>71.83</v>
       </c>
       <c r="H5" t="n">
-        <v>93.22</v>
+        <v>94.37</v>
       </c>
       <c r="I5" t="n">
-        <v>108.68</v>
+        <v>141.37</v>
       </c>
       <c r="J5" t="n">
-        <v>128.25</v>
+        <v>175.78</v>
       </c>
       <c r="K5" t="n">
-        <v>60.41</v>
+        <v>109.33</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.74</v>
+        <v>2.62</v>
       </c>
       <c r="D6" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="E6" t="n">
-        <v>24.88</v>
+        <v>27.01</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="G6" t="n">
-        <v>2.69</v>
+        <v>2.17</v>
       </c>
       <c r="H6" t="n">
-        <v>4.21</v>
+        <v>2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>2.71</v>
       </c>
       <c r="J6" t="n">
-        <v>4.98</v>
+        <v>4.45</v>
       </c>
       <c r="K6" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
